--- a/ArchivoProgram/insumos_movimientos.xlsx
+++ b/ArchivoProgram/insumos_movimientos.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Listado de Insumos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Distritos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Presentaciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="SAN PEDRO AYAMPUC" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="PALENCIA" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="SAN JOSE DEL GOLFO" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listado de Insumos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Distritos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Presentaciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SAN PEDRO AYAMPUC" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PALENCIA" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SAN JOSE DEL GOLFO" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1" iterate="1"/>
@@ -1099,10 +1099,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="7"/>
+    <col width="14" customWidth="1" min="1" max="7"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
@@ -1157,12 +1157,12 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>AJAX</t>
+          <t>AMONIO GALON</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>CAJA</t>
+          <t>PAQUETE</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
@@ -1172,27 +1172,69 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>-5.0</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>45.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>CLORO GALON</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>PAQUETE</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>-10.0</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>40.0</t>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>6.0</t>
         </is>
       </c>
     </row>
